--- a/src/templates/users_import.xlsx
+++ b/src/templates/users_import.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Truong Lam\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Truong Lam\Documents\pj\da\src\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3797E6F-AD95-40FE-807F-C989F31F63F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD92C12E-FB7C-4ADB-93E5-D6D32DCBF939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="16">
   <si>
     <t>email</t>
   </si>
@@ -62,6 +62,12 @@
   </si>
   <si>
     <t>HS161457</t>
+  </si>
+  <si>
+    <t>class</t>
+  </si>
+  <si>
+    <t>Lớp 1</t>
   </si>
 </sst>
 </file>
@@ -429,10 +435,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="45.5703125" customWidth="1"/>
+    <col min="4" max="4" width="33.5703125" customWidth="1"/>
+    <col min="5" max="5" width="65.140625" customWidth="1"/>
+    <col min="6" max="6" width="58.28515625" customWidth="1"/>
+    <col min="7" max="7" width="51.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -443,25 +456,28 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -472,22 +488,25 @@
         <v>12</v>
       </c>
       <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
         <v>13</v>
       </c>
-      <c r="E2" t="b">
+      <c r="F2" t="b">
         <v>0</v>
       </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
       <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
         <v>2025</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -498,22 +517,25 @@
         <v>12</v>
       </c>
       <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
         <v>13</v>
       </c>
-      <c r="E3" t="b">
+      <c r="F3" t="b">
         <v>0</v>
       </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
       <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
         <v>2025</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -524,18 +546,21 @@
         <v>12</v>
       </c>
       <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
         <v>13</v>
       </c>
-      <c r="E4" t="b">
+      <c r="F4" t="b">
         <v>0</v>
       </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
       <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
         <v>2025</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>1</v>
       </c>
     </row>
